--- a/Tests/representative_network_2_sim_outputs.xlsx
+++ b/Tests/representative_network_2_sim_outputs.xlsx
@@ -390,7 +390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.77734375" customWidth="1" min="1" max="5"/>
@@ -753,6 +753,6462 @@
         <v>36.75710413157911</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>17</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3453.607059029783</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1473.476712301373</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>12159.05464333296</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>28.880648963157</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>15670.40289242093</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>39.49706922067708</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>37791.60268290106</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>4.328706710274446</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.657356800000003</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>2.670682749450522</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>0.0006671608239133675</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>17</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>15654.49745816328</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1663.424764310918</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>35241.13354173836</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>3.247205812010662</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.859443911111114</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>1.387211821604156</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>0.0005500792953038531</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4266.808964388821</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>43.63642041414278</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>21298.98234759213</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>10.84755137759556</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.219200888888821</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>9.604905740151725</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>0.02344474855486131</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>17</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5910.72850152317</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1083.04824854678</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>23078.68072864143</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>16.93081178641729</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.238761979174221</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>10.67750481342971</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>0.0145449938128206</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4746.013198839524</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1517.737618336861</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>22603.39529399315</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>12.16761873445235</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.143524799999951</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>11.00689249440786</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>0.01720144004428729</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>17</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6988.522037416613</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1166.267141390833</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>53032.69125668606</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>10.21962519533109</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.203370666666621</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>8.994928924920076</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>0.02132560374423007</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>17</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5914.370046132877</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1524.594421674148</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>37516.5531085066</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>12.21318433532271</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.54055733333329</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>10.65464647262417</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>0.01798052936513617</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>17</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6068.416190978623</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1514.466007757554</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>33649.67906798999</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>10.07294376347681</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.434768115673282</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>8.621981168506791</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>0.01619447929661581</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="n">
+        <v>17</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5542.937248426781</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1071.502428201773</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>15031.50739292114</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>14.0508949135078</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.393834942502503</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>12.64016342315519</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>0.01689654784994568</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4960.818787169449</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>38.54080261409399</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>17864.06994812406</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>12.91370220296945</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.423935822222182</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>11.47822492341198</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>0.01154145733474143</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>100</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6700.354379717019</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>41.5838803727529</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>22035.57865821559</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>12.39454900066717</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.585108799999954</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>10.79861683927697</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>0.01082336139004075</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>5058.050133881256</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>38.25304346732446</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>23863.0503235202</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>12.78606876492496</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.49795359999996</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>11.27215290386041</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>0.01596226106468336</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4314.2032299402</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1517.380209997995</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>15023.67318412074</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>12.56625988262337</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.288674027654219</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>11.26254882369545</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>0.01503703127319478</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5122.584199031679</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>37.09161773591768</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>15030.96586093641</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>15.51842249874021</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.703449244444398</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>13.79882428115903</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>0.01614897313644787</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
+        <v>17</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>6089.6934713515</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1521.074132942391</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>27079.81433597279</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>10.84598676374587</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.489063644444395</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>9.343554544442274</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>0.01336857485896046</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>4994.860520363541</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>45.27479448009399</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>29044.75345951802</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>15.15908756781013</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.666600711111059</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>13.4791549350404</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>0.01333192165827245</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="n">
+        <v>17</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>7540.879887518987</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>47.77078117820201</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>27643.52846671056</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>13.31952206640091</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.809768888888851</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>11.49872218333718</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>0.01103099417473672</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="n">
+        <v>17</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>100</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>5149.14478049658</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>73.45439042366343</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>15042.73322460818</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>14.37763709509677</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.556057345589893</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>12.80530288026941</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>0.01627686923719555</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="n">
+        <v>17</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>100</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>5921.009344125738</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1503.332058994827</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>39350.57019734022</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>13.39467823272375</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.200752177777736</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>12.1811920269708</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
+        <v>0.01273402797490277</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>17</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>100</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>7978.72226182254</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1514.045551023795</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>47555.33981035597</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>16.8862583326125</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.504637688888833</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>15.36536002445737</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
+        <v>0.01626061926598894</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="n">
+        <v>17</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>100</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>5646.637892322567</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1512.672283235821</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>33023.18762497761</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>14.26369147039895</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.420321955555522</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>12.82721049747807</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>0.01615901736499872</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="n">
+        <v>17</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>5143.883536565199</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>68.03043479457847</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>19108.92843733658</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>14.02908354865352</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.472916541617135</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>12.53914606264905</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>0.01702094438713454</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
+        <v>17</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>100</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>4641.071210535632</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>36.13881596415013</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>14523.49603658781</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>11.79343559486948</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.304118933333293</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>10.47807282581596</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>0.01124383571969445</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="n">
+        <v>17</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>100</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>4658.254818890499</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>36.70560492109507</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>23278.85695269145</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>13.23091939979719</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.494308444444393</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>11.71976994021598</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>0.01684101513626967</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="n">
+        <v>17</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>600000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>100</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>3482.359043734371</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1515.051151317544</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>14074.86222320376</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>17.71045674164399</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.356356207691862</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>16.11678120798538</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>0.237319325967019</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="n">
+        <v>17</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>100</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>4928.535043632887</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1506.201334824786</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>21915.8974375712</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>23.69704709117396</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.112338311114394</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>20.23026854090346</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>1.354440239157188</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="n">
+        <v>17</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>100</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>4000.716824046313</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1507.801095975563</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>14063.4116217983</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>22.17464196442674</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.624212088891277</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>19.20646325563983</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>1.343966619897063</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="n">
+        <v>17</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>3845.214353595017</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>1507.678750216961</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>14066.12505233474</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>22.62129664268319</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.564219555559016</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>19.59799036986726</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>1.459086717258414</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="n">
+        <v>17</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>4124.601867632256</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1498.550070652738</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>16125.63535191864</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>15.73014427893864</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.726120000002792</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>12.66052797569995</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>1.343496303237221</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" t="n">
+        <v>17</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E38" t="n">
+        <v>100</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>3574.399623796288</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1509.131928213872</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>14076.96361918375</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>15.25668185973133</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.36453973333611</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>12.66407868970539</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>1.228063436690562</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" t="n">
+        <v>17</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E39" t="n">
+        <v>100</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>3543.238088704022</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>1507.627028997988</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>15040.03316067904</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>12.81298611957099</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.218363911113408</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>10.23150774067398</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>1.363114467784038</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="n">
+        <v>17</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>100</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>4250.909880678714</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>1493.923824960366</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>15164.95655135065</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>14.1230618043639</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.688538133335271</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
+        <v>11.11833063192164</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>1.316193039108239</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" t="n">
+        <v>17</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E41" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>3691.01827561553</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>1509.455906204879</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>14336.74665420875</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>16.42831164118253</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.658694400003817</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S41" t="n">
+        <v>13.25070111060205</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>1.518916130577562</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="n">
+        <v>17</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E42" t="n">
+        <v>100</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>4768.942376938496</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>1037.487459516153</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>22150.14947084198</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>20.24726652732684</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>7.78553208889167</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>11.28464698644308</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>1.177087451993171</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="n">
+        <v>17</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E43" t="n">
+        <v>100</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>4225.423475887027</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>2022.81594344601</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>8042.439201123867</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>18.93606315032586</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>7.003298133337061</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S43" t="n">
+        <v>10.5672196590726</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>1.36554535791752</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" t="n">
+        <v>17</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E44" t="n">
+        <v>100</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>3953.742799630594</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1504.697872169316</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>16002.3971840525</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>17.52544348836881</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.604509866669681</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S44" t="n">
+        <v>14.62928716408121</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>1.29164645761946</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" t="n">
+        <v>17</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E45" t="n">
+        <v>100</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>3694.48464688469</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1436.916126430035</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>14980.14720236044</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>15.8126757616253</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.751861688891233</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S45" t="n">
+        <v>11.79020027108404</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>1.270613801650853</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" t="n">
+        <v>17</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E46" t="n">
+        <v>100</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>3798.553267002895</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1050.319740084</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>14003.62737625465</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>16.52873160134736</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.98069688889337</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>11.83122559079156</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>1.716809121663454</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="n">
+        <v>17</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E47" t="n">
+        <v>100</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>3564.140734277044</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1447.292826902121</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>11986.49711807072</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>17.98904686708828</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.769582933335662</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
+        <v>14.03049760379244</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>1.18896632996083</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" t="n">
+        <v>17</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E48" t="n">
+        <v>100</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>3954.926408977715</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>1335.014209609479</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>22540.45209834998</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>18.13337856420347</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.928717134897673</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
+        <v>13.74956488128075</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>1.455096548026252</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" t="n">
+        <v>17</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E49" t="n">
+        <v>100</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>3515.990503409653</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>1369.905634135008</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>14042.20928748883</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>15.00702400863302</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.34586097778035</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S49" t="n">
+        <v>11.35523278035044</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>1.305930250503126</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="n">
+        <v>17</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E50" t="n">
+        <v>100</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>4261.933673518904</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>1385.955845076591</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>14074.68535215966</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>15.47095273816078</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.912592711113325</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>11.06925714621914</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>1.489102880828914</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="n">
+        <v>17</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E51" t="n">
+        <v>100</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>4670.331877235507</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1364.259755915031</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>14161.54584395513</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>14.23804807242583</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.745560888890839</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>10.18662478591556</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>1.305862397620238</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="n">
+        <v>17</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E52" t="n">
+        <v>100</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>4254.874078263195</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1375.073352592997</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>19490.08843479957</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>16.92044307338178</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.15758275555841</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S52" t="n">
+        <v>12.32563760414636</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>1.437222713678285</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="n">
+        <v>17</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>360000</v>
+      </c>
+      <c r="E53" t="n">
+        <v>100</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>4038.953601200806</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>1506.804740910418</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>20072.08986053802</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>13.3330342995779</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>1.531067760744848</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
+        <v>11.66710704481118</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
+        <v>0.134859494021267</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" t="n">
+        <v>17</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>360000</v>
+      </c>
+      <c r="E54" t="n">
+        <v>100</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>4859.49512831733</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>1498.232567763422</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>18452.10432335688</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>12.55453949243613</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.630280177777673</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
+        <v>10.79691878904235</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
+        <v>0.1273405256153405</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" t="n">
+        <v>17</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>360000</v>
+      </c>
+      <c r="E55" t="n">
+        <v>100</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>4755.895530293897</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>1504.555789103673</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>18534.82818139711</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>23.76867106005804</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.748388578627335</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S55" t="n">
+        <v>21.88334387975322</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>0.1369386016772648</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" t="n">
+        <v>17</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>360000</v>
+      </c>
+      <c r="E56" t="n">
+        <v>100</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>3911.989222731275</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>1502.495762902545</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>14104.81865581824</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>24.02793448866628</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>1.579470933333353</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S56" t="n">
+        <v>22.31874311136599</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
+        <v>0.1297204439668845</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57" t="n">
+        <v>17</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" t="n">
+        <v>360000</v>
+      </c>
+      <c r="E57" t="n">
+        <v>100</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>4428.973940442401</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1510.910832808469</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>19949.23382790689</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>23.13475197300373</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.656611733333404</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S57" t="n">
+        <v>21.34665879286502</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
+        <v>0.1314814468053303</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" t="n">
+        <v>17</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="n">
+        <v>360000</v>
+      </c>
+      <c r="E58" t="n">
+        <v>100</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>4609.658323760897</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>1510.336693553487</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>20063.64038199373</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>22.77147844983075</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>1.626789511111078</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S58" t="n">
+        <v>21.02046099798892</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
+        <v>0.1242279407302816</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" t="n">
+        <v>17</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="n">
+        <v>360000</v>
+      </c>
+      <c r="E59" t="n">
+        <v>100</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>4345.109567120277</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>42.36996998390532</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>16103.94961143238</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>39.81271279568983</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>1.463044977777731</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S59" t="n">
+        <v>38.25543553372061</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
+        <v>0.09423228419109157</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" t="n">
+        <v>17</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="n">
+        <v>360000</v>
+      </c>
+      <c r="E60" t="n">
+        <v>100</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>4564.128428827798</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>40.77503368584439</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>19510.82830144884</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>46.58713959610995</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>1.666886222222391</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S60" t="n">
+        <v>44.79213402732926</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
+        <v>0.128119346558038</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B61" t="n">
+        <v>17</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="n">
+        <v>360000</v>
+      </c>
+      <c r="E61" t="n">
+        <v>100</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>4418.185080608604</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>1498.931747001596</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>19579.74068905669</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>41.46807615551363</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>1.588536888888755</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S61" t="n">
+        <v>39.79757871448512</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>0.08196055213958986</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" t="n">
+        <v>17</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E62" t="n">
+        <v>100</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>8201.576596849454</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>57.3248536036117</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>44610.50517958525</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>12.54450553811473</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>1.756771377777752</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S62" t="n">
+        <v>10.78087722285131</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
+        <v>0.006856937485801524</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" t="n">
+        <v>17</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E63" t="n">
+        <v>100</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>7960.415910906175</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>1517.89489871425</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>24986.94302826139</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>12.68905383478638</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>1.691375644444418</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S63" t="n">
+        <v>10.99044515036477</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
+        <v>0.007233039977163015</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1</v>
+      </c>
+      <c r="B64" t="n">
+        <v>17</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E64" t="n">
+        <v>100</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>7754.114292111298</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>344.531309529033</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>28130.4269082998</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>9.470320076803574</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>1.621667201447057</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S64" t="n">
+        <v>7.841561600509853</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
+        <v>0.007091274846663415</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" t="n">
+        <v>17</v>
+      </c>
+      <c r="C65" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E65" t="n">
+        <v>100</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>7491.037504561248</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>1493.753990252473</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>28256.32576294227</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>11.91281791300409</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>1.807903425684095</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S65" t="n">
+        <v>10.09842204622903</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
+        <v>0.006492441090831895</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" t="n">
+        <v>17</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E66" t="n">
+        <v>100</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>6990.239883599547</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>38.73887198472221</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>24941.83286363377</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>7.618408132778299</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>1.469758399999982</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S66" t="n">
+        <v>6.142207588740552</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
+        <v>0.006442144037395942</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" t="n">
+        <v>17</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E67" t="n">
+        <v>100</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>9143.994696296662</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>86.32284689665539</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>41602.37875100981</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>10.86995548012186</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>1.777073955555532</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S67" t="n">
+        <v>9.084360010583573</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>0.008521513982533667</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" t="n">
+        <v>17</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E68" t="n">
+        <v>100</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>7508.619543313809</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>56.08356282117529</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>23534.60892192275</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>9.463880573059726</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>1.781855288888871</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S68" t="n">
+        <v>7.676284248410013</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>0.00574103576061013</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" t="n">
+        <v>17</v>
+      </c>
+      <c r="C69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E69" t="n">
+        <v>100</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>7447.878536189821</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>114.0992258549959</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>30080.18439925145</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>8.908703506651463</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>1.580687288888863</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S69" t="n">
+        <v>7.319458298179663</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>0.008557919582622385</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" t="n">
+        <v>17</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E70" t="n">
+        <v>100</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>7381.332048966296</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>1451.313580283604</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>23033.63428730186</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>8.625685289279232</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>1.620494577777757</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S70" t="n">
+        <v>6.997019580378164</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>0.008171131123086936</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" t="n">
+        <v>17</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E71" t="n">
+        <v>100</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>5473.820985797747</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1199.220485453057</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>30036.27540951153</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>8.71672345909198</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>1.374004911636652</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S71" t="n">
+        <v>7.332916993879159</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>0.0098015535758663</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" t="n">
+        <v>17</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" t="n">
+        <v>360000</v>
+      </c>
+      <c r="E72" t="n">
+        <v>100</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>4578.171052455876</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>1504.873362979037</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>14108.37148205959</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>14.81880890096338</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>1.590455288888782</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S72" t="n">
+        <v>13.10236654527128</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>0.1259870668034302</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" t="n">
+        <v>17</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E73" t="n">
+        <v>100</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>3543.655998034091</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>35.05166684277356</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>18765.53610116616</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>14.87562078509609</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>3.121275911113511</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S73" t="n">
+        <v>10.21782454102083</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
+        <v>1.53652033296235</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1</v>
+      </c>
+      <c r="B74" t="n">
+        <v>17</v>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E74" t="n">
+        <v>100</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>3913.194499396866</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>1414.005708025768</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>13023.60696320608</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>17.0327746957704</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>2.836605688891816</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S74" t="n">
+        <v>12.85873799759951</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>1.337431009280336</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1</v>
+      </c>
+      <c r="B75" t="n">
+        <v>17</v>
+      </c>
+      <c r="C75" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E75" t="n">
+        <v>100</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3684.338201231777</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>1368.274689646438</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>11991.283148624</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>19.29490801844842</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>2.84216924444753</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S75" t="n">
+        <v>14.85795915737414</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U75" t="n">
+        <v>1.594779616627732</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" t="n">
+        <v>17</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E76" t="n">
+        <v>100</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>4185.64298614386</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>1361.867680218071</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>13052.92649158277</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>21.98058215118297</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.952024533335864</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S76" t="n">
+        <v>17.35774501771458</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U76" t="n">
+        <v>1.670812600133631</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" t="n">
+        <v>17</v>
+      </c>
+      <c r="C77" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E77" t="n">
+        <v>100</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>3378.933312204814</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>1047.026382382028</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>13024.31476848572</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>19.50483985246501</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>2.951156266669978</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S77" t="n">
+        <v>14.66013605170214</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
+        <v>1.893547534093794</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1</v>
+      </c>
+      <c r="B78" t="n">
+        <v>17</v>
+      </c>
+      <c r="C78" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E78" t="n">
+        <v>100</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>3553.228270590141</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>1386.394243284129</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>13062.21239415463</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>14.4011452643186</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>2.924200888892094</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S78" t="n">
+        <v>9.763351290780301</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U78" t="n">
+        <v>1.713593084647384</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1</v>
+      </c>
+      <c r="B79" t="n">
+        <v>17</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E79" t="n">
+        <v>100</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>3589.505955971988</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>1340.628083977848</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>18462.25012452714</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>15.42801162607435</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>2.814173511113718</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S79" t="n">
+        <v>11.20307796156058</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U79" t="n">
+        <v>1.410760153401486</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B80" t="n">
+        <v>17</v>
+      </c>
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E80" t="n">
+        <v>100</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>3894.357611339597</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>1317.979202520102</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>13057.38217333518</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>16.66766443672786</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>2.78478542222507</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S80" t="n">
+        <v>12.4106892393629</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U80" t="n">
+        <v>1.472189775141205</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1</v>
+      </c>
+      <c r="B81" t="n">
+        <v>17</v>
+      </c>
+      <c r="C81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E81" t="n">
+        <v>300</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0.9866666666666667</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>3616.680445051019</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>160.757033444941</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>14066.62140545622</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>51.72188649635325</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>8.150223644410755</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S81" t="n">
+        <v>38.9686910936699</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U81" t="n">
+        <v>4.602971758275899</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1</v>
+      </c>
+      <c r="B82" t="n">
+        <v>17</v>
+      </c>
+      <c r="C82" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E82" t="n">
+        <v>500</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>3912.106434034775</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1284.330107070506</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>22112.21093909978</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>84.83785643669077</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>13.44368676764187</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S82" t="n">
+        <v>63.98942411866054</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U82" t="n">
+        <v>7.404745550395216</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" t="n">
+        <v>17</v>
+      </c>
+      <c r="C83" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E83" t="n">
+        <v>500</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>4348.256307182653</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>43.31655786931515</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>8039.734008267522</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>89.93187810737064</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>34.76836195558653</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S83" t="n">
+        <v>47.77684616740288</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U83" t="n">
+        <v>7.386669984386687</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1</v>
+      </c>
+      <c r="B84" t="n">
+        <v>17</v>
+      </c>
+      <c r="C84" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E84" t="n">
+        <v>500</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>3912.656972519032</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1346.465675115585</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>21493.29525880143</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>87.13366612898866</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>13.1227790222488</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S84" t="n">
+        <v>66.62515195339253</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U84" t="n">
+        <v>7.385735153354263</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1</v>
+      </c>
+      <c r="B85" t="n">
+        <v>17</v>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E85" t="n">
+        <v>500</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>3790.493356271067</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1341.849591553211</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>15049.90701182187</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>87.49631318914679</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>11.83447271114136</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S85" t="n">
+        <v>68.36778571351566</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U85" t="n">
+        <v>7.294054764496552</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1</v>
+      </c>
+      <c r="B86" t="n">
+        <v>17</v>
+      </c>
+      <c r="C86" t="n">
+        <v>3</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E86" t="n">
+        <v>500</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>3960.339083978106</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>1040.07733764872</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>23784.38533674181</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>112.0365019029481</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>40.61553955557161</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S86" t="n">
+        <v>64.52554793194315</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U86" t="n">
+        <v>6.895414415439912</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1</v>
+      </c>
+      <c r="B87" t="n">
+        <v>17</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E87" t="n">
+        <v>500</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>3554.334895443164</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>1037.546500897501</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>17912.37659968436</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>---&gt; Total Power:</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>97.50695144174841</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TX:</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>35.33439514727242</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RX:</t>
+        </is>
+      </c>
+      <c r="S87" t="n">
+        <v>54.88110737929892</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAD:</t>
+        </is>
+      </c>
+      <c r="U87" t="n">
+        <v>7.291448915182854</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
